--- a/data/regional_child_rearing_support_base/data.xlsx
+++ b/data/regional_child_rearing_support_base/data.xlsx
@@ -472,7 +472,7 @@
         <v>16：00</v>
       </c>
       <c r="L2" t="str">
-        <v>利用可能時間は10:00～12:00、13:00～16:00（12:00～13:00は休み時間）</v>
+        <v>利用可能時間は10:00～12:00、13:00～16:00</v>
       </c>
     </row>
     <row r="3">
@@ -685,7 +685,7 @@
         <v>087-816-7700</v>
       </c>
       <c r="G8" t="str">
-        <v>http://himawarinet.c.ooco.jp/policy.html</v>
+        <v>https://himawarinet.hp.peraichi.com/1</v>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -738,7 +738,7 @@
         <v>15：30</v>
       </c>
       <c r="L9" t="str">
-        <v>利用可能時間は09:30～12:00、13:00～15:30</v>
+        <v>12:00～13:00制限あり。月１回程度度、土・日・祝日開所</v>
       </c>
     </row>
     <row r="10">
@@ -773,7 +773,7 @@
         <v>10:00</v>
       </c>
       <c r="K10" t="str">
-        <v>15:30</v>
+        <v>15:00</v>
       </c>
       <c r="L10" t="str">
         <v/>
